--- a/TestFiles/ExcelFiles/LevelOfCare.xlsx
+++ b/TestFiles/ExcelFiles/LevelOfCare.xlsx
@@ -86,7 +86,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="n">
-        <v>10.73</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="2">
@@ -94,7 +94,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>11.6</v>
+        <v>7.78</v>
       </c>
     </row>
     <row r="3">
@@ -102,7 +102,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>11.73</v>
+        <v>9.26</v>
       </c>
     </row>
     <row r="4">
@@ -110,7 +110,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>11.82</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="5">
@@ -118,7 +118,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>8.96</v>
+        <v>12.37</v>
       </c>
     </row>
   </sheetData>

--- a/TestFiles/ExcelFiles/LevelOfCare.xlsx
+++ b/TestFiles/ExcelFiles/LevelOfCare.xlsx
@@ -86,7 +86,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="n">
-        <v>4.01</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="2">
@@ -94,7 +94,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>3.51</v>
+        <v>11.86</v>
       </c>
     </row>
     <row r="3">
@@ -102,7 +102,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>5.04</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="4">
@@ -110,7 +110,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>9.8</v>
+        <v>9.14</v>
       </c>
     </row>
     <row r="5">
@@ -118,7 +118,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>11.72</v>
+        <v>2.99</v>
       </c>
     </row>
   </sheetData>
